--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484294_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484294_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3208</v>
+        <v>6.1768</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9191</v>
+        <v>3.0202</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4018</v>
+        <v>3.1566</v>
       </c>
       <c r="G2" t="n">
         <v>5.1465</v>
@@ -610,13 +610,13 @@
         <v>2.1488</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6973</v>
+        <v>-0.8413</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4525</v>
+        <v>-1.3514</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7553</v>
+        <v>0.5102</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2772</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2087</v>
+        <v>3.6833</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1031</v>
+        <v>0.3054</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1056</v>
+        <v>3.3779</v>
       </c>
       <c r="G3" t="n">
         <v>4.5507</v>
@@ -688,13 +688,13 @@
         <v>2.3441</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4555</v>
+        <v>-0.9809</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4525</v>
+        <v>-1.2503</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0029</v>
+        <v>0.2694</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2772</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1221</v>
+        <v>3.3278</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5006</v>
+        <v>4.4866</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6226</v>
+        <v>-1.1588</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9336</v>
+        <v>1.5091</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1046</v>
+        <v>0.1878</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0383</v>
+        <v>1.3214</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4285</v>
+        <v>4.3707</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3338</v>
+        <v>1.6999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09470000000000001</v>
+        <v>2.6707</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5051</v>
+        <v>-2.8615</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4384</v>
+        <v>-1.5121</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9435</v>
+        <v>-1.3494</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3441</v>
+        <v>2.1488</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0655</v>
+        <v>-0.5916</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.839</v>
+        <v>-0.6451</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7734</v>
+        <v>0.0535</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8865</v>
+        <v>2.2149</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8865</v>
+        <v>2.7145</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.4996</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0923</v>
+        <v>2.4997</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2239</v>
+        <v>-0.905</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1316</v>
+        <v>3.4048</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5091</v>
+        <v>0.9336</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1878</v>
+        <v>-0.1046</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3214</v>
+        <v>1.0383</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3707</v>
+        <v>0.4285</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6999</v>
+        <v>0.3338</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6707</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.8615</v>
+        <v>0.5051</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5121</v>
+        <v>-0.4384</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3494</v>
+        <v>0.9435</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1488</v>
+        <v>2.3441</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.6879</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-1.2434</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0808</v>
+        <v>0.5556</v>
       </c>
       <c r="V5" t="n">
-        <v>2.2149</v>
+        <v>0.8865</v>
       </c>
       <c r="W5" t="n">
-        <v>2.7145</v>
+        <v>0.8865</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>S. ROMEO FO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5612</v>
+        <v>2.3566</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3221</v>
+        <v>1.0554</v>
       </c>
       <c r="F6" t="n">
-        <v>0.239</v>
+        <v>1.3012</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6152</v>
+        <v>1.6317</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3981</v>
+        <v>1.5505</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7829</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1089</v>
+        <v>1.2974</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9471</v>
+        <v>1.3507</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1619</v>
+        <v>-0.0533</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4937</v>
+        <v>0.3342</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.549</v>
+        <v>0.1998</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9447</v>
+        <v>0.1344</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8325</v>
+        <v>-0.0565</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1899</v>
+        <v>-0.2421</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.1856</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. ROMEO FO</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4867</v>
+        <v>2.0732</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9948</v>
+        <v>2.0793</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4919</v>
+        <v>-0.0061</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6317</v>
+        <v>1.6152</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5505</v>
+        <v>2.3981</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08110000000000001</v>
+        <v>-0.7829</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2974</v>
+        <v>3.1089</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3507</v>
+        <v>2.9471</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0533</v>
+        <v>0.1619</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3342</v>
+        <v>-1.4937</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1998</v>
+        <v>-0.549</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1344</v>
+        <v>-0.9447</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0737</v>
+        <v>0.3446</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3026</v>
+        <v>-0.0529</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3763</v>
+        <v>0.3975</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5533</v>
+        <v>2.0067</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9689</v>
+        <v>2.2316</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4156</v>
+        <v>-0.2249</v>
       </c>
       <c r="G8" t="n">
         <v>0.473</v>
@@ -1078,13 +1078,13 @@
         <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.701</v>
+        <v>-0.2476</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.4635</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0253</v>
+        <v>0.2159</v>
       </c>
       <c r="V8" t="n">
         <v>0.6093</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1986</v>
+        <v>1.5448</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9587</v>
+        <v>-1.8576</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1573</v>
+        <v>3.4024</v>
       </c>
       <c r="G9" t="n">
         <v>1.9999</v>
@@ -1156,13 +1156,13 @@
         <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8133</v>
+        <v>-0.4671</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0894</v>
+        <v>-0.9883</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2761</v>
+        <v>0.5212</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5507</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2633</v>
+        <v>0.7651</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.187</v>
+        <v>0.0152</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4503</v>
+        <v>0.7499</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2061</v>
@@ -1234,13 +1234,13 @@
         <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0934</v>
+        <v>-0.5916</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6052</v>
+        <v>-0.403</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4881</v>
+        <v>-0.1886</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. SELLARÈS GIRALT</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2984</v>
+        <v>-0.416</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2107</v>
+        <v>-1.2776</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9123</v>
+        <v>0.8617</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1502</v>
+        <v>-0.5054</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7114</v>
+        <v>-0.3167</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.8616</v>
+        <v>-0.1887</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6133999999999999</v>
+        <v>-0.4908</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1256</v>
+        <v>0.1023</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5122</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7636</v>
+        <v>-0.0146</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4142</v>
+        <v>-0.419</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3494</v>
+        <v>0.4045</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3907</v>
+        <v>0.3907</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5783</v>
+        <v>-0.3013</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1294</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4489</v>
+        <v>0.4855</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>D. TORRALBA CAROZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3887</v>
+        <v>-0.5637</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2776</v>
+        <v>-0.7951</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8889</v>
+        <v>0.2314</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5054</v>
+        <v>-0.7439</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3167</v>
+        <v>-0.8788</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1887</v>
+        <v>0.1348</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4908</v>
+        <v>-0.6741</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1023</v>
+        <v>-0.6741</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0146</v>
+        <v>-0.0698</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.419</v>
+        <v>-0.2047</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4045</v>
+        <v>0.1348</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.274</v>
+        <v>-0.0151</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.121</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5128</v>
+        <v>0.1059</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. TORRALBA CAROZ</t>
+          <t>M. SELLARÈS GIRALT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.591</v>
+        <v>-0.6229</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.7951</v>
+        <v>-1.4535</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2042</v>
+        <v>0.8306</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7439</v>
+        <v>-1.1502</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8788</v>
+        <v>0.7114</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1348</v>
+        <v>-1.8616</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6741</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6741</v>
+        <v>1.1256</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0.5122</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0698</v>
+        <v>-1.7636</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2047</v>
+        <v>-0.4142</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1348</v>
+        <v>-1.3494</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0424</v>
+        <v>0.2538</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.121</v>
+        <v>-0.1134</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.3672</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="14">
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>22.5289</v>
+        <v>22.8314</v>
       </c>
       <c r="E14" t="n">
-        <v>6.602200000000002</v>
+        <v>6.9049</v>
       </c>
       <c r="F14" t="n">
         <v>15.9267</v>
@@ -1513,7 +1513,7 @@
         <v>15.2541</v>
       </c>
       <c r="H14" t="n">
-        <v>9.859299999999999</v>
+        <v>9.859299999999998</v>
       </c>
       <c r="I14" t="n">
         <v>5.394700000000002</v>
@@ -1528,13 +1528,13 @@
         <v>5.400600000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.943199999999999</v>
+        <v>-4.9432</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.937099999999999</v>
+        <v>-4.9371</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.005899999999999878</v>
+        <v>-0.005899999999999794</v>
       </c>
       <c r="P14" t="n">
         <v>9.767099999999999</v>
@@ -1546,13 +1546,13 @@
         <v>18.5575</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.484999999999999</v>
+        <v>-4.182500000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-7.963799999999999</v>
+        <v>-7.661200000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>3.4792</v>
+        <v>3.4789</v>
       </c>
       <c r="V14" t="n">
         <v>1.9926</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6423</v>
+        <v>1.3428</v>
       </c>
       <c r="E15" t="n">
         <v>-0.1483</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7907</v>
+        <v>1.4911</v>
       </c>
       <c r="G15" t="n">
         <v>0.1215</v>
@@ -1624,13 +1624,13 @@
         <v>0.1953</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6614</v>
+        <v>0.3618</v>
       </c>
       <c r="T15" t="n">
         <v>-0.3494</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0107</v>
+        <v>0.7111</v>
       </c>
       <c r="V15" t="n">
         <v>0.6642</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>M. PACÍFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0418</v>
+        <v>-0.499</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3753</v>
+        <v>0.7806</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3335</v>
+        <v>-1.2796</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.3167</v>
+        <v>1.068</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.7892</v>
+        <v>-0.6718</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4726</v>
+        <v>1.7398</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9445</v>
+        <v>2.2462</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.8774999999999999</v>
+        <v>0.3709</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8219</v>
+        <v>1.8752</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.2611</v>
+        <v>-1.1781</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.9118</v>
+        <v>-1.0427</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3494</v>
+        <v>-0.1354</v>
       </c>
       <c r="P16" t="n">
         <v>0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7725</v>
+        <v>0.2841</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4308</v>
+        <v>-0.4889</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3416</v>
+        <v>0.773</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0906</v>
+        <v>-0.9154</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8564</v>
+        <v>-1.7553</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7659</v>
+        <v>0.8399</v>
       </c>
       <c r="G17" t="n">
         <v>-1.7456</v>
@@ -1780,13 +1780,13 @@
         <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8587</v>
+        <v>1.0338</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8857</v>
+        <v>-0.7846</v>
       </c>
       <c r="U17" t="n">
-        <v>2.7444</v>
+        <v>1.8184</v>
       </c>
       <c r="V17" t="n">
         <v>1.1638</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5382</v>
+        <v>-1.051</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2862</v>
+        <v>1.3642</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8243</v>
+        <v>-2.4152</v>
       </c>
       <c r="G18" t="n">
-        <v>1.068</v>
+        <v>-2.3167</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6718</v>
+        <v>-2.7892</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7398</v>
+        <v>0.4726</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2462</v>
+        <v>0.9445</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3709</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8752</v>
+        <v>1.8219</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1781</v>
+        <v>-3.2611</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0427</v>
+        <v>-1.9118</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1354</v>
+        <v>-1.3494</v>
       </c>
       <c r="P18" t="n">
         <v>0.586</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S18" t="n">
-        <v>0.245</v>
+        <v>0.6796</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0167</v>
+        <v>0.4197</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2283</v>
+        <v>0.2599</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7571</v>
+        <v>-1.3642</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6176</v>
+        <v>-0.4153</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1395</v>
+        <v>-0.9489</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6931</v>
@@ -1936,13 +1936,13 @@
         <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4314</v>
+        <v>-0.0385</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4237</v>
+        <v>-0.2214</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0077</v>
+        <v>0.1829</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2186</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0932</v>
+        <v>-1.3776</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1237</v>
+        <v>-0.517</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9695</v>
+        <v>-0.8606</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1032</v>
@@ -2014,13 +2014,13 @@
         <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0013</v>
+        <v>-0.3946</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9062</v>
+        <v>1.0151</v>
       </c>
       <c r="V20" t="n">
         <v>0.2772</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. GASPAR AGUILAR</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8704</v>
+        <v>-2.8626</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.412</v>
+        <v>-0.62</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4584</v>
+        <v>-2.2426</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5278</v>
+        <v>-1.4994</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3387</v>
+        <v>0.1325</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1891</v>
+        <v>-1.6319</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2248</v>
+        <v>1.2419</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3057</v>
+        <v>1.9289</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0809</v>
+        <v>-0.6869</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.303</v>
+        <v>-2.7413</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.033</v>
+        <v>-1.7964</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.27</v>
+        <v>-0.9449</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5627</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2202</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2337</v>
+        <v>-0.4276</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4539</v>
+        <v>1.0178</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>F. GASPAR AGUILAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3372</v>
+        <v>-3.0375</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8222</v>
+        <v>-2.7153</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.515</v>
+        <v>-0.3222</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4994</v>
+        <v>-1.5278</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1325</v>
+        <v>-1.3387</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6319</v>
+        <v>-0.1891</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2419</v>
+        <v>-0.2248</v>
       </c>
       <c r="K22" t="n">
-        <v>1.9289</v>
+        <v>-0.3057</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6869</v>
+        <v>0.0809</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7413</v>
+        <v>-1.303</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7964</v>
+        <v>-1.033</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9449</v>
+        <v>-0.27</v>
       </c>
       <c r="P22" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-1.9534</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-2.9301</v>
-      </c>
       <c r="R22" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1156</v>
+        <v>0.053</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6299</v>
+        <v>-0.5371</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.5901</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.0225</v>
+        <v>-5.6102</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.425</v>
+        <v>-5.1217</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5975</v>
+        <v>-0.4885</v>
       </c>
       <c r="G23" t="n">
         <v>0.7457</v>
@@ -2248,13 +2248,13 @@
         <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0484</v>
+        <v>0.3639</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5172</v>
+        <v>-0.2138</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4687</v>
+        <v>0.5777</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6642</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.504</v>
+        <v>-7.154</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.183</v>
+        <v>-6.7785</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.321</v>
+        <v>-0.3755</v>
       </c>
       <c r="G24" t="n">
         <v>-8.303599999999999</v>
@@ -2326,13 +2326,13 @@
         <v>1.3674</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1866</v>
+        <v>0.5366</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8857</v>
+        <v>-0.4813</v>
       </c>
       <c r="U24" t="n">
-        <v>1.0723</v>
+        <v>1.0178</v>
       </c>
       <c r="V24" t="n">
         <v>0.2224</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-22.5291</v>
+        <v>-22.5287</v>
       </c>
       <c r="E25" t="n">
-        <v>-15.9267</v>
+        <v>-15.9266</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.6021</v>
+        <v>-6.602099999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-15.2542</v>
@@ -2404,13 +2404,13 @@
         <v>8.790299999999998</v>
       </c>
       <c r="S25" t="n">
-        <v>4.484999999999999</v>
+        <v>4.485</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.4791</v>
+        <v>-3.479</v>
       </c>
       <c r="U25" t="n">
-        <v>7.963900000000001</v>
+        <v>7.9638</v>
       </c>
       <c r="V25" t="n">
         <v>-1.9925</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484294_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484294_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -721,67 +736,72 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3278</v>
+        <v>3.6559</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4866</v>
+        <v>3.6559</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1588</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5091</v>
+        <v>3.6559</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1878</v>
+        <v>1.2279</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3214</v>
+        <v>2.4279</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3707</v>
+        <v>3.6559</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6999</v>
+        <v>1.2279</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6707</v>
+        <v>2.4279</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.8615</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5121</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3494</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5916</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6451</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0535</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>2.2149</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4996</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,11 +1296,16 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.416</v>
+        <v>-0.3281</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2776</v>
+        <v>0.8308</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8617</v>
+        <v>-1.1588</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5054</v>
+        <v>-2.1468</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3167</v>
+        <v>-1.0402</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1887</v>
+        <v>-1.1066</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4908</v>
+        <v>0.7148</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1023</v>
+        <v>0.472</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.2428</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0146</v>
+        <v>-2.8615</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.419</v>
+        <v>-1.5121</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4045</v>
+        <v>-1.3494</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3907</v>
+        <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3013</v>
+        <v>-0.5916</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.6451</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4855</v>
+        <v>0.0535</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>2.2149</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.4996</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. TORRALBA CAROZ</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1400,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5637</v>
+        <v>-0.416</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7951</v>
+        <v>-1.2776</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2314</v>
+        <v>0.8617</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7439</v>
+        <v>-0.5054</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8788</v>
+        <v>-0.3167</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1348</v>
+        <v>-0.1887</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6741</v>
+        <v>-0.4908</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6741</v>
+        <v>0.1023</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0698</v>
+        <v>-0.0146</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2047</v>
+        <v>-0.419</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1348</v>
+        <v>0.4045</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0151</v>
+        <v>-0.3013</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.121</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1059</v>
+        <v>0.4855</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1406,12 +1461,17 @@
       </c>
       <c r="X12" t="n">
         <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. SELLARÈS GIRALT</t>
+          <t>D. TORRALBA CAROZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6229</v>
+        <v>-0.5637</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4535</v>
+        <v>-0.7951</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8306</v>
+        <v>0.2314</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.1502</v>
+        <v>-0.7439</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7114</v>
+        <v>-0.8788</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8616</v>
+        <v>0.1348</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6133999999999999</v>
+        <v>-0.6741</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1256</v>
+        <v>-0.6741</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5122</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7636</v>
+        <v>-0.0698</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4142</v>
+        <v>-0.2047</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3494</v>
+        <v>0.1348</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2538</v>
+        <v>-0.0151</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1134</v>
+        <v>-0.121</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3672</v>
+        <v>0.1059</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SELLARES GIRALT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,151 +1566,157 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>22.8314</v>
+        <v>-0.6229</v>
       </c>
       <c r="E14" t="n">
-        <v>6.9049</v>
+        <v>-1.4535</v>
       </c>
       <c r="F14" t="n">
-        <v>15.9267</v>
+        <v>0.8306</v>
       </c>
       <c r="G14" t="n">
-        <v>15.2541</v>
+        <v>-1.1502</v>
       </c>
       <c r="H14" t="n">
-        <v>9.859299999999998</v>
+        <v>0.7114</v>
       </c>
       <c r="I14" t="n">
-        <v>5.394700000000002</v>
+        <v>-1.8616</v>
       </c>
       <c r="J14" t="n">
-        <v>20.1972</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>14.7965</v>
+        <v>1.1256</v>
       </c>
       <c r="L14" t="n">
-        <v>5.400600000000001</v>
+        <v>-0.5122</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.9432</v>
+        <v>-1.7636</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.9371</v>
+        <v>-0.4142</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.005899999999999794</v>
+        <v>-1.3494</v>
       </c>
       <c r="P14" t="n">
-        <v>9.767099999999999</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8.7903</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>18.5575</v>
+        <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.182500000000001</v>
+        <v>0.2538</v>
       </c>
       <c r="T14" t="n">
-        <v>-7.661200000000001</v>
+        <v>-0.1134</v>
       </c>
       <c r="U14" t="n">
-        <v>3.4789</v>
+        <v>0.3672</v>
       </c>
       <c r="V14" t="n">
-        <v>1.9926</v>
+        <v>0.6642</v>
       </c>
       <c r="W14" t="n">
-        <v>3.1592</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.1667</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. KOTSEV</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C.B. CUARTE DE HUERVA</t>
+          <t>TENEA-C.B. ESPARREGUERA</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3428</v>
+        <v>22.8314</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1483</v>
+        <v>6.904999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4911</v>
+        <v>15.9267</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1215</v>
+        <v>15.2541</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0653</v>
+        <v>9.859199999999998</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1867</v>
+        <v>5.394600000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.201</v>
+        <v>20.1972</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4464</v>
+        <v>14.7965</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6475</v>
+        <v>5.400600000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0795</v>
+        <v>-4.9432</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6188</v>
+        <v>-4.9371</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5393</v>
+        <v>-0.005899999999999794</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1953</v>
+        <v>9.767099999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-8.7903</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1953</v>
+        <v>18.5575</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3618</v>
+        <v>-4.182500000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3494</v>
+        <v>-7.661200000000003</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7111</v>
+        <v>3.4789</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6642</v>
+        <v>1.9926</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.1592</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6642</v>
-      </c>
+        <v>-1.1667</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>M. KOTSEV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.499</v>
+        <v>1.3428</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7806</v>
+        <v>-0.1483</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2796</v>
+        <v>1.4911</v>
       </c>
       <c r="G16" t="n">
-        <v>1.068</v>
+        <v>0.1215</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6718</v>
+        <v>-1.0653</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7398</v>
+        <v>1.1867</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2462</v>
+        <v>0.201</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3709</v>
+        <v>-0.4464</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8752</v>
+        <v>0.6475</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1781</v>
+        <v>-0.0795</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0427</v>
+        <v>-0.6188</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1354</v>
+        <v>0.5393</v>
       </c>
       <c r="P16" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2841</v>
+        <v>0.3618</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4889</v>
+        <v>-0.3494</v>
       </c>
       <c r="U16" t="n">
-        <v>0.773</v>
+        <v>0.7111</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.4373</v>
+        <v>0.6642</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.4373</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>M. PACIFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9154</v>
+        <v>-0.499</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7553</v>
+        <v>0.7806</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8399</v>
+        <v>-1.2796</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7456</v>
+        <v>1.068</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0867</v>
+        <v>-0.6718</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6589</v>
+        <v>1.7398</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7957</v>
+        <v>2.2462</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0491</v>
+        <v>0.3709</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2535</v>
+        <v>1.8752</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5413</v>
+        <v>-1.1781</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.1358</v>
+        <v>-1.0427</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4054</v>
+        <v>-0.1354</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
         <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0338</v>
+        <v>0.2841</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7846</v>
+        <v>-0.4889</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8184</v>
+        <v>0.773</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1638</v>
+        <v>-2.4373</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.051</v>
+        <v>-0.9154</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3642</v>
+        <v>-1.7553</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.4152</v>
+        <v>0.8399</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.3167</v>
+        <v>-1.7456</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.7892</v>
+        <v>-0.0867</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4726</v>
+        <v>-1.6589</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9445</v>
+        <v>0.7957</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8774999999999999</v>
+        <v>2.0491</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8219</v>
+        <v>-1.2535</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.2611</v>
+        <v>-2.5413</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.9118</v>
+        <v>-2.1358</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3494</v>
+        <v>-0.4054</v>
       </c>
       <c r="P18" t="n">
-        <v>0.586</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6796</v>
+        <v>1.0338</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4197</v>
+        <v>-0.7846</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2599</v>
+        <v>1.8184</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. LOPEZ SANCHEZ</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1977,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3642</v>
+        <v>-1.051</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4153</v>
+        <v>1.3642</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9489</v>
+        <v>-2.4152</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6931</v>
+        <v>-2.3167</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4635</v>
+        <v>-2.7892</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2296</v>
+        <v>0.4726</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4702</v>
+        <v>0.9445</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4298</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0405</v>
+        <v>1.8219</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1634</v>
+        <v>-3.2611</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8933</v>
+        <v>-1.9118</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.27</v>
+        <v>-1.3494</v>
       </c>
       <c r="P19" t="n">
         <v>0.586</v>
@@ -1936,28 +2022,33 @@
         <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0385</v>
+        <v>0.6796</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2214</v>
+        <v>0.4197</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1829</v>
+        <v>0.2599</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>O. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3776</v>
+        <v>-1.3642</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.517</v>
+        <v>-0.4153</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8606</v>
+        <v>-0.9489</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1032</v>
+        <v>-0.6931</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.968</v>
+        <v>-0.4635</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1352</v>
+        <v>-0.2296</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5538</v>
+        <v>0.4702</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2047</v>
+        <v>0.4298</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3492</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.6571</v>
+        <v>-1.1634</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1727</v>
+        <v>-0.8933</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4844</v>
+        <v>-0.27</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6205000000000001</v>
+        <v>-0.0385</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3946</v>
+        <v>-0.2214</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0151</v>
+        <v>0.1829</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2772</v>
+        <v>-1.2186</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8626</v>
+        <v>-1.3776</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.62</v>
+        <v>-0.517</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2426</v>
+        <v>-0.8606</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4994</v>
+        <v>-1.1032</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1325</v>
+        <v>-0.968</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6319</v>
+        <v>-0.1352</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2419</v>
+        <v>1.5538</v>
       </c>
       <c r="K21" t="n">
-        <v>1.9289</v>
+        <v>0.2047</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6869</v>
+        <v>1.3492</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7413</v>
+        <v>-2.6571</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7964</v>
+        <v>-1.1727</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9449</v>
+        <v>-1.4844</v>
       </c>
       <c r="P21" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-1.9534</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-2.9301</v>
-      </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4276</v>
+        <v>-0.3946</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0178</v>
+        <v>1.0151</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4959</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. GASPAR AGUILAR</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0375</v>
+        <v>-2.8626</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7153</v>
+        <v>-0.62</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3222</v>
+        <v>-2.2426</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5278</v>
+        <v>-1.4994</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3387</v>
+        <v>0.1325</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1891</v>
+        <v>-1.6319</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2248</v>
+        <v>1.2419</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3057</v>
+        <v>1.9289</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0809</v>
+        <v>-0.6869</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.303</v>
+        <v>-2.7413</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.033</v>
+        <v>-1.7964</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.27</v>
+        <v>-0.9449</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5627</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>0.053</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5371</v>
+        <v>-0.4276</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5901</v>
+        <v>1.0178</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. CLEDJO HOUNGUES</t>
+          <t>F. GASPAR AGUILAR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6102</v>
+        <v>-3.0375</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.1217</v>
+        <v>-2.7153</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4885</v>
+        <v>-0.3222</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7457</v>
+        <v>-1.5278</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2315</v>
+        <v>-1.3387</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4858</v>
+        <v>-0.1891</v>
       </c>
       <c r="J23" t="n">
-        <v>2.5933</v>
+        <v>-0.2248</v>
       </c>
       <c r="K23" t="n">
-        <v>2.539</v>
+        <v>-0.3057</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0543</v>
+        <v>0.0809</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8476</v>
+        <v>-1.303</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3075</v>
+        <v>-1.033</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5401</v>
+        <v>-0.27</v>
       </c>
       <c r="P23" t="n">
-        <v>-6.0556</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q23" t="n">
-        <v>-6.837</v>
+        <v>-1.9534</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3639</v>
+        <v>0.053</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2138</v>
+        <v>-0.5371</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5777</v>
+        <v>0.5901</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>N. CLEDJO HOUNGUES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.154</v>
+        <v>-5.6102</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.7785</v>
+        <v>-5.1217</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3755</v>
+        <v>-0.4885</v>
       </c>
       <c r="G24" t="n">
-        <v>-8.303599999999999</v>
+        <v>0.7457</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.8402</v>
+        <v>1.2315</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.4635</v>
+        <v>-0.4858</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.8787</v>
+        <v>2.5933</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9555</v>
+        <v>2.539</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.9232</v>
+        <v>0.0543</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.4249</v>
+        <v>-1.8476</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.8846</v>
+        <v>-1.3075</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5403</v>
+        <v>-0.5401</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3907</v>
+        <v>-6.0556</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9767</v>
+        <v>-6.837</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5366</v>
+        <v>0.3639</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4813</v>
+        <v>-0.2138</v>
       </c>
       <c r="U24" t="n">
-        <v>1.0178</v>
+        <v>0.5777</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2224</v>
+        <v>-0.6642</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.4418</v>
+        <v>-0.6642</v>
       </c>
       <c r="X24" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,152 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-7.154</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-6.7785</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.3755</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-8.303599999999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-3.8402</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-4.4635</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-4.8787</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.9555</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-3.9232</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-3.4249</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-2.8846</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.5403</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.5366</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.4813</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.0178</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.2224</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.4418</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484294_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>-22.5287</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E26" t="n">
         <v>-15.9266</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F26" t="n">
         <v>-6.602099999999999</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G26" t="n">
         <v>-15.2542</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H26" t="n">
         <v>-9.859399999999999</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I26" t="n">
         <v>-5.3949</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J26" t="n">
         <v>4.943099999999999</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K26" t="n">
         <v>4.9373</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L26" t="n">
         <v>0.005900000000000016</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M26" t="n">
         <v>-20.1973</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N26" t="n">
         <v>-14.7966</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O26" t="n">
         <v>-5.4006</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P26" t="n">
         <v>-9.767199999999999</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q26" t="n">
         <v>-18.5574</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>8.790299999999998</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>4.485</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>-3.479</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>7.9638</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V26" t="n">
         <v>-1.9925</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W26" t="n">
         <v>1.1667</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X26" t="n">
         <v>-3.1593</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
